--- a/Infusion_Pumps_India/Infusion_Pump_Classification_India.xlsx
+++ b/Infusion_Pumps_India/Infusion_Pump_Classification_India.xlsx
@@ -104,7 +104,7 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="00FFF59D"/>
+        <fgColor rgb="00FCE4D6"/>
       </patternFill>
     </fill>
     <fill>
@@ -236,7 +236,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="34">
+  <cellXfs count="35">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
@@ -262,7 +262,7 @@
     <xf numFmtId="0" fontId="3" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="3" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="5" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
@@ -270,7 +270,7 @@
     <xf numFmtId="0" fontId="3" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="3" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
@@ -283,16 +283,19 @@
     <xf numFmtId="0" fontId="7" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="3" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="7" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="7" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="8" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
@@ -814,10 +817,9 @@
       </c>
       <c r="C6" s="13" t="inlineStr">
         <is>
-          <t>EUR 9.40B FY25 group sales (~USD 10.79B*)
-Hospital Care div.: EUR 5.09B
-India entity FY25: INR 500-750 Cr
-(see Revenue tab)</t>
+          <t>EUR 9.40B FY25 group sales (~USD 10.53B*)
+of which Hospital Care div. (incl. infusion therapy): EUR 5.09B
+Source: B. Braun Annual Report 2025</t>
         </is>
       </c>
       <c r="D6" s="14" t="inlineStr">
@@ -830,11 +832,7 @@
           <t>Perfusor compactplus**</t>
         </is>
       </c>
-      <c r="F6" s="15" t="inlineStr">
-        <is>
-          <t>Spaceplus Perfusor (not verified in India)</t>
-        </is>
-      </c>
+      <c r="F6" s="15" t="n"/>
       <c r="G6" s="14" t="inlineStr">
         <is>
           <t>Infusomat fmS</t>
@@ -854,7 +852,7 @@
         <is>
           <t>- Standard columns were blank: add Perfusor compact, compact S, Infusomat fmS, Infusomat P
 - compactplus &amp; Space pumps -&gt; Smart** (connectivity is optional)
-- 'Perfusor Space Plus' NOT on India catalogue -&gt; remove/footnote
+- 'Perfusor Space Plus' removed: not offered in India (catalogue + distributors)
 - 'Infusomat Space' -&gt; India lists Infusomat Space P
 - 'Infusomat Space Place' typo -&gt; Spaceplus Infusomat
 - Add Infusomat compactplus P</t>
@@ -863,7 +861,7 @@
       <c r="K6" s="16" t="n"/>
       <c r="L6" s="4" t="inlineStr">
         <is>
-          <t>Not verified in India - needs manual check / remove</t>
+          <t>Pending confirmation of an Indian distributor listing</t>
         </is>
       </c>
     </row>
@@ -881,7 +879,7 @@
           <t>Perfusor Space**</t>
         </is>
       </c>
-      <c r="F7" s="18" t="n"/>
+      <c r="F7" s="17" t="n"/>
       <c r="G7" s="14" t="inlineStr">
         <is>
           <t>Infusomat P</t>
@@ -901,7 +899,7 @@
       <c r="C8" s="10" t="n"/>
       <c r="D8" s="18" t="n"/>
       <c r="E8" s="18" t="n"/>
-      <c r="F8" s="18" t="n"/>
+      <c r="F8" s="10" t="n"/>
       <c r="G8" s="18" t="n"/>
       <c r="H8" s="14" t="inlineStr">
         <is>
@@ -924,13 +922,12 @@
       </c>
       <c r="C9" s="13" t="inlineStr">
         <is>
-          <t>EUR 8.61B FY25 Kabi revenue (~USD 9.89B*)
-MedTech: EUR 1.61B
-India entity FY25: INR 750-1,000 Cr
-(see Revenue tab)</t>
-        </is>
-      </c>
-      <c r="D9" s="19" t="n"/>
+          <t>EUR 8.61B FY25 Kabi revenue (~USD 9.65B*)
+of which MedTech (incl. infusion pumps): EUR 1.61B
+Source: Fresenius Annual Report 2025</t>
+        </is>
+      </c>
+      <c r="D9" s="15" t="n"/>
       <c r="E9" s="14" t="inlineStr">
         <is>
           <t>Infusia SP7s (SP7sED3)</t>
@@ -941,22 +938,22 @@
           <t>Agilia SP MC WiFi</t>
         </is>
       </c>
-      <c r="G9" s="19" t="n"/>
+      <c r="G9" s="15" t="n"/>
       <c r="H9" s="14" t="inlineStr">
         <is>
           <t>Infusia VP7s (VP7sED3)</t>
         </is>
       </c>
-      <c r="I9" s="15" t="inlineStr">
-        <is>
-          <t>Agilia VP MC WiFi (not verified in India)</t>
+      <c r="I9" s="19" t="inlineStr">
+        <is>
+          <t>Agilia VP MC WiFi (pending India confirmation)</t>
         </is>
       </c>
       <c r="J9" s="13" t="inlineStr">
         <is>
           <t>- Add Agilia SP (Smart), Agilia SP MC &amp; SP TIVA (Smart**)
-- Agilia VP (distributor only) -&gt; Volumetric Smart, yellow
-- Agilia VP MC WiFi: no India listing found -&gt; verify or remove
+- Agilia VP (distributor only) -&gt; Volumetric Smart, peach
+- Agilia VP MC WiFi: pending distributor confirmation (keep only if an Indian listing is found)
 - Infusia SP7s/VP7s &amp; Agilia SP MC WiFi confirmed</t>
         </is>
       </c>
@@ -1016,7 +1013,7 @@
     <row r="14">
       <c r="A14" s="21" t="inlineStr">
         <is>
-          <t>** Smart** = drug library + connectivity optional (separately sold data module / WiFi variant).  * USD at EUR/USD 1.148, the rate implied by the sample slide - confirm FX basis (see Revenue tab).</t>
+          <t>** Smart** = drug library + connectivity optional (separately sold data module / WiFi variant).  * USD converted at ECB EUR/USD reference rate 1.1204 (5-Oct-2026), latest available; sample slide had used ~1.148.</t>
         </is>
       </c>
     </row>
@@ -1028,7 +1025,7 @@
       </c>
     </row>
   </sheetData>
-  <mergeCells count="14">
+  <mergeCells count="15">
     <mergeCell ref="J9:J12"/>
     <mergeCell ref="D9:D12"/>
     <mergeCell ref="C9:C12"/>
@@ -1043,6 +1040,7 @@
     <mergeCell ref="A4:C4"/>
     <mergeCell ref="A6:A8"/>
     <mergeCell ref="B6:B8"/>
+    <mergeCell ref="F6:F8"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -1431,12 +1429,12 @@
       </c>
       <c r="F6" s="12" t="inlineStr">
         <is>
-          <t>Connected (global only)</t>
+          <t>Excluded - not offered in India</t>
         </is>
       </c>
       <c r="G6" s="24" t="inlineStr">
         <is>
-          <t>Not verified in India</t>
+          <t>Not offered in India</t>
         </is>
       </c>
       <c r="H6" s="25" t="inlineStr">
@@ -1456,7 +1454,7 @@
       </c>
       <c r="K6" s="13" t="inlineStr">
         <is>
-          <t>REMOVE from India matrix (not listed on India catalogue) or footnote as global-only</t>
+          <t>REMOVED - not on B. Braun India catalogue; not found on Indian distributor sites (confirmed by project team, manual check)</t>
         </is>
       </c>
       <c r="L6" s="13" t="inlineStr">
@@ -2299,7 +2297,7 @@
       </c>
       <c r="K19" s="13" t="inlineStr">
         <is>
-          <t>ADD to Volumetric-Smart (yellow - distributor only)</t>
+          <t>ADD to Volumetric-Smart (peach - distributor only)</t>
         </is>
       </c>
       <c r="L19" s="13" t="inlineStr">
@@ -2319,7 +2317,7 @@
           <t>Fresenius Kabi</t>
         </is>
       </c>
-      <c r="B20" s="24" t="inlineStr">
+      <c r="B20" s="28" t="inlineStr">
         <is>
           <t>Agilia VP MC WiFi</t>
         </is>
@@ -2344,14 +2342,14 @@
           <t>Connected (global only)</t>
         </is>
       </c>
-      <c r="G20" s="24" t="inlineStr">
+      <c r="G20" s="28" t="inlineStr">
         <is>
           <t>Not verified in India</t>
         </is>
       </c>
-      <c r="H20" s="24" t="inlineStr">
-        <is>
-          <t>None found - not on FK India site or Arraymed</t>
+      <c r="H20" s="28" t="inlineStr">
+        <is>
+          <t>Pending - not on FK India site or Arraymed; IndiaMart search for team check: https://dir.indiamart.com/search.mp?ss=agilia+vp+mc+wifi</t>
         </is>
       </c>
       <c r="I20" s="13" t="inlineStr">
@@ -2366,7 +2364,7 @@
       </c>
       <c r="K20" s="13" t="inlineStr">
         <is>
-          <t>UNVERIFIED - provide the IndiaMart/distributor link, or remove</t>
+          <t>PENDING team confirmation of IndiaMart/distributor listing; remove if none</t>
         </is>
       </c>
       <c r="L20" s="13" t="inlineStr">
@@ -2429,7 +2427,7 @@
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" s="28" t="inlineStr">
+      <c r="A1" s="29" t="inlineStr">
         <is>
           <t>Revenue cross-check (FY2025)</t>
         </is>
@@ -2441,12 +2439,12 @@
           <t>EUR/USD rate (input)</t>
         </is>
       </c>
-      <c r="B2" s="29" t="n">
-        <v>1.148</v>
+      <c r="B2" s="30" t="n">
+        <v>1.1204</v>
       </c>
       <c r="C2" s="2" t="inlineStr">
         <is>
-          <t>Assumption: rate implied by sample slide (USD 10.79B / EUR 9.396B = USD 9.89B / EUR 8.612B = 1.148). Confirm whether average or closing rate is intended and replace.</t>
+          <t>ECB euro reference rate, latest available (5-Oct-2026): https://data.ecb.europa.eu/data/datasets/EXR/EXR.D.USD.EUR.SP00.A  |  For reference: 2025 annual average 1.1300; the sample slide implied ~1.148.</t>
         </is>
       </c>
     </row>
@@ -2523,10 +2521,10 @@
           <t>FY2025 (Dec-25)</t>
         </is>
       </c>
-      <c r="D5" s="30" t="n">
+      <c r="D5" s="31" t="n">
         <v>9396</v>
       </c>
-      <c r="E5" s="31">
+      <c r="E5" s="32">
         <f>IF(D5="","n/a",D5*$B$2/1000)</f>
         <v/>
       </c>
@@ -2537,7 +2535,7 @@
       </c>
       <c r="G5" s="13" t="inlineStr">
         <is>
-          <t>Matches (EUR 9,396mn x 1.148)</t>
+          <t>EUR figure matches; sample USD used ~1.148 -&gt; now USD 10.53B at latest ECB rate</t>
         </is>
       </c>
       <c r="H5" s="13" t="inlineStr">
@@ -2572,10 +2570,10 @@
           <t>FY2025</t>
         </is>
       </c>
-      <c r="D6" s="30" t="n">
+      <c r="D6" s="31" t="n">
         <v>5090.8</v>
       </c>
-      <c r="E6" s="31">
+      <c r="E6" s="32">
         <f>IF(D6="","n/a",D6*$B$2/1000)</f>
         <v/>
       </c>
@@ -2621,8 +2619,8 @@
           <t>FY2025 (Mar-25)</t>
         </is>
       </c>
-      <c r="D7" s="30" t="n"/>
-      <c r="E7" s="31">
+      <c r="D7" s="31" t="n"/>
+      <c r="E7" s="32">
         <f>IF(D7="","n/a",D7*$B$2/1000)</f>
         <v/>
       </c>
@@ -2633,7 +2631,7 @@
       </c>
       <c r="G7" s="13" t="inlineStr">
         <is>
-          <t>Not on sample</t>
+          <t>UNOFFICIAL - not used on slide</t>
         </is>
       </c>
       <c r="H7" s="13" t="inlineStr">
@@ -2668,10 +2666,10 @@
           <t>FY2025 (Dec-25)</t>
         </is>
       </c>
-      <c r="D8" s="30" t="n">
+      <c r="D8" s="31" t="n">
         <v>8612</v>
       </c>
-      <c r="E8" s="31">
+      <c r="E8" s="32">
         <f>IF(D8="","n/a",D8*$B$2/1000)</f>
         <v/>
       </c>
@@ -2682,7 +2680,7 @@
       </c>
       <c r="G8" s="13" t="inlineStr">
         <is>
-          <t>Matches (EUR 8,612mn x 1.148)</t>
+          <t>EUR figure matches; sample USD used ~1.148 -&gt; now USD 9.65B at latest ECB rate</t>
         </is>
       </c>
       <c r="H8" s="13" t="inlineStr">
@@ -2717,10 +2715,10 @@
           <t>FY2025</t>
         </is>
       </c>
-      <c r="D9" s="30" t="n">
+      <c r="D9" s="31" t="n">
         <v>1610</v>
       </c>
-      <c r="E9" s="31">
+      <c r="E9" s="32">
         <f>IF(D9="","n/a",D9*$B$2/1000)</f>
         <v/>
       </c>
@@ -2766,8 +2764,8 @@
           <t>FY2025 (Mar-25)</t>
         </is>
       </c>
-      <c r="D10" s="30" t="n"/>
-      <c r="E10" s="31">
+      <c r="D10" s="31" t="n"/>
+      <c r="E10" s="32">
         <f>IF(D10="","n/a",D10*$B$2/1000)</f>
         <v/>
       </c>
@@ -2778,7 +2776,7 @@
       </c>
       <c r="G10" s="13" t="inlineStr">
         <is>
-          <t>Not on sample</t>
+          <t>UNOFFICIAL - not used on slide</t>
         </is>
       </c>
       <c r="H10" s="13" t="inlineStr">
@@ -2870,7 +2868,7 @@
           <t>India catalogue - automated infusion systems (master list)</t>
         </is>
       </c>
-      <c r="C2" s="32" t="inlineStr">
+      <c r="C2" s="33" t="inlineStr">
         <is>
           <t>https://catalogs.bbraun.co.in/en-IN/c/PRODUCTS0000000529/automated-infusion-systems</t>
         </is>
@@ -2902,7 +2900,7 @@
           <t>Perfusor compact</t>
         </is>
       </c>
-      <c r="C3" s="32" t="inlineStr">
+      <c r="C3" s="33" t="inlineStr">
         <is>
           <t>https://catalogs.bbraun.co.in/en-IN/p/PRID00000461</t>
         </is>
@@ -2934,7 +2932,7 @@
           <t>Perfusor compact S</t>
         </is>
       </c>
-      <c r="C4" s="32" t="inlineStr">
+      <c r="C4" s="33" t="inlineStr">
         <is>
           <t>https://catalogs.bbraun.co.in/en-IN/p/PRID00000145</t>
         </is>
@@ -2966,7 +2964,7 @@
           <t>Perfusor compactplus</t>
         </is>
       </c>
-      <c r="C5" s="32" t="inlineStr">
+      <c r="C5" s="33" t="inlineStr">
         <is>
           <t>https://catalogs.bbraun.co.in/en-IN/p/PRID00010216</t>
         </is>
@@ -2998,7 +2996,7 @@
           <t>Data module compactplus (connectivity add-on)</t>
         </is>
       </c>
-      <c r="C6" s="32" t="inlineStr">
+      <c r="C6" s="33" t="inlineStr">
         <is>
           <t>https://catalogs.bbraun.co.in/en-IN/p/PRID00011150</t>
         </is>
@@ -3030,7 +3028,7 @@
           <t>compactplus brochure (p.5 data module, p.6 DoseGuard)</t>
         </is>
       </c>
-      <c r="C7" s="32" t="inlineStr">
+      <c r="C7" s="33" t="inlineStr">
         <is>
           <t>https://ecatalog.bbraun.com/eDoc/QlBSMDAwMDAwMDAwMDAwMDAwMTAwMDE4NTA5OTAwMDAw?openInline=true</t>
         </is>
@@ -3058,7 +3056,7 @@
           <t>Perfusor Space</t>
         </is>
       </c>
-      <c r="C8" s="32" t="inlineStr">
+      <c r="C8" s="33" t="inlineStr">
         <is>
           <t>https://catalogs.bbraun.co.in/en-IN/p/PRID00001226</t>
         </is>
@@ -3090,7 +3088,7 @@
           <t>Infusomat fmS</t>
         </is>
       </c>
-      <c r="C9" s="32" t="inlineStr">
+      <c r="C9" s="33" t="inlineStr">
         <is>
           <t>https://catalogs.bbraun.co.in/en-IN/p/PRID00000618</t>
         </is>
@@ -3122,7 +3120,7 @@
           <t>Infusomat P</t>
         </is>
       </c>
-      <c r="C10" s="32" t="inlineStr">
+      <c r="C10" s="33" t="inlineStr">
         <is>
           <t>https://catalogs.bbraun.co.in/en-IN/p/PRID00000689</t>
         </is>
@@ -3154,7 +3152,7 @@
           <t>Infusomat compactplus</t>
         </is>
       </c>
-      <c r="C11" s="32" t="inlineStr">
+      <c r="C11" s="33" t="inlineStr">
         <is>
           <t>https://catalogs.bbraun.co.in/en-IN/p/PRID00011042</t>
         </is>
@@ -3186,7 +3184,7 @@
           <t>Infusomat compactplus P</t>
         </is>
       </c>
-      <c r="C12" s="32" t="inlineStr">
+      <c r="C12" s="33" t="inlineStr">
         <is>
           <t>https://catalogs.bbraun.co.in/en-IN/p/PRID00012086</t>
         </is>
@@ -3214,7 +3212,7 @@
           <t>Infusomat Space P</t>
         </is>
       </c>
-      <c r="C13" s="32" t="inlineStr">
+      <c r="C13" s="33" t="inlineStr">
         <is>
           <t>https://catalogs.bbraun.co.in/en-IN/p/PRID00001230</t>
         </is>
@@ -3242,7 +3240,7 @@
           <t>Spaceplus Infusomat</t>
         </is>
       </c>
-      <c r="C14" s="32" t="inlineStr">
+      <c r="C14" s="33" t="inlineStr">
         <is>
           <t>https://catalogs.bbraun.co.in/en-IN/p/PRID00011860</t>
         </is>
@@ -3274,7 +3272,7 @@
           <t>Annual Report 2025 (revenue)</t>
         </is>
       </c>
-      <c r="C15" s="32" t="inlineStr">
+      <c r="C15" s="33" t="inlineStr">
         <is>
           <t>https://www.bbraun.com/en/about-us/company/facts-and-figures/annual-report.html</t>
         </is>
@@ -3306,7 +3304,7 @@
           <t>Annual Report 2025 PDF (p.8, p.43)</t>
         </is>
       </c>
-      <c r="C16" s="32" t="inlineStr">
+      <c r="C16" s="33" t="inlineStr">
         <is>
           <t>https://www.bbraun.com/content/dam/b-braun/master/website-6/en/04_about-us/0401_company/facts-and-figures/2025_B_Braun_Annual_Report.pdf</t>
         </is>
@@ -3338,7 +3336,7 @@
           <t>India entity financials</t>
         </is>
       </c>
-      <c r="C17" s="32" t="inlineStr">
+      <c r="C17" s="33" t="inlineStr">
         <is>
           <t>https://www.tofler.in/b-braun-medical-india-private-limited/company/U33112MH1984PTC214514</t>
         </is>
@@ -3370,7 +3368,7 @@
           <t>compactplus system (global page)</t>
         </is>
       </c>
-      <c r="C18" s="32" t="inlineStr">
+      <c r="C18" s="33" t="inlineStr">
         <is>
           <t>https://www.bbraun.com/en/products-and-solutions/therapies/infusion-therapy/automated-infusion-systems/compactplus-system.html</t>
         </is>
@@ -3380,7 +3378,7 @@
           <t>Global website</t>
         </is>
       </c>
-      <c r="E18" s="24" t="inlineStr">
+      <c r="E18" s="28" t="inlineStr">
         <is>
           <t>DROP</t>
         </is>
@@ -3402,7 +3400,7 @@
           <t>Spaceplus Perfusor (global catalogue)</t>
         </is>
       </c>
-      <c r="C19" s="32" t="inlineStr">
+      <c r="C19" s="33" t="inlineStr">
         <is>
           <t>https://catalogs.bbraun.com/en-01/p/PRID00011858/spaceplus-perfusor</t>
         </is>
@@ -3412,7 +3410,7 @@
           <t>Global website</t>
         </is>
       </c>
-      <c r="E19" s="24" t="inlineStr">
+      <c r="E19" s="28" t="inlineStr">
         <is>
           <t>DROP</t>
         </is>
@@ -3434,7 +3432,7 @@
           <t>India - Infusion Therapy (navigation)</t>
         </is>
       </c>
-      <c r="C20" s="32" t="inlineStr">
+      <c r="C20" s="33" t="inlineStr">
         <is>
           <t>https://www.fresenius-kabi.com/in/products/ins/infusion-therapy</t>
         </is>
@@ -3466,7 +3464,7 @@
           <t>India - Agilia range (lists SP, SP MC, SP TIVA only)</t>
         </is>
       </c>
-      <c r="C21" s="32" t="inlineStr">
+      <c r="C21" s="33" t="inlineStr">
         <is>
           <t>https://www.fresenius-kabi.com/in/products/ins/infusion-therapy/agilia-range</t>
         </is>
@@ -3498,7 +3496,7 @@
           <t>India - Infusia range</t>
         </is>
       </c>
-      <c r="C22" s="32" t="inlineStr">
+      <c r="C22" s="33" t="inlineStr">
         <is>
           <t>https://www.fresenius-kabi.com/in/products/ins/infusion-therapy/infusia-range</t>
         </is>
@@ -3526,7 +3524,7 @@
           <t>Infusia SP7s</t>
         </is>
       </c>
-      <c r="C23" s="32" t="inlineStr">
+      <c r="C23" s="33" t="inlineStr">
         <is>
           <t>https://www.fresenius-kabi.com/in/products/ins/infusion-therapy/infusia-range/infusia-sp7sed3</t>
         </is>
@@ -3558,7 +3556,7 @@
           <t>Infusia VP7s</t>
         </is>
       </c>
-      <c r="C24" s="32" t="inlineStr">
+      <c r="C24" s="33" t="inlineStr">
         <is>
           <t>https://www.fresenius-kabi.com/in/products/ins/infusion-therapy/infusia-range/infusia-vp7sed3</t>
         </is>
@@ -3586,7 +3584,7 @@
           <t>Agilia SP</t>
         </is>
       </c>
-      <c r="C25" s="32" t="inlineStr">
+      <c r="C25" s="33" t="inlineStr">
         <is>
           <t>https://www.fresenius-kabi.com/in/products/ins/infusion-therapy/agilia-range/agilia-sp</t>
         </is>
@@ -3614,7 +3612,7 @@
           <t>Agilia SP MC / SP MC WiFi</t>
         </is>
       </c>
-      <c r="C26" s="32" t="inlineStr">
+      <c r="C26" s="33" t="inlineStr">
         <is>
           <t>https://www.fresenius-kabi.com/in/products/ins/infusion-therapy/agilia-range/agilia-sp-mc</t>
         </is>
@@ -3646,7 +3644,7 @@
           <t>Agilia SP TIVA</t>
         </is>
       </c>
-      <c r="C27" s="32" t="inlineStr">
+      <c r="C27" s="33" t="inlineStr">
         <is>
           <t>https://www.fresenius-kabi.com/in/products/ins/infusion-therapy/agilia-range/agilia-sp-tiva</t>
         </is>
@@ -3674,7 +3672,7 @@
           <t>Agilia VP (distributor)</t>
         </is>
       </c>
-      <c r="C28" s="32" t="inlineStr">
+      <c r="C28" s="33" t="inlineStr">
         <is>
           <t>https://arraymed.co.in/product/fresenius-kabi-agilia-vp/</t>
         </is>
@@ -3686,7 +3684,7 @@
       </c>
       <c r="E28" s="13" t="inlineStr">
         <is>
-          <t>KEEP (yellow)</t>
+          <t>KEEP (peach)</t>
         </is>
       </c>
       <c r="F28" s="13" t="inlineStr">
@@ -3706,7 +3704,7 @@
           <t>Agilia SP (drug-library evidence)</t>
         </is>
       </c>
-      <c r="C29" s="32" t="inlineStr">
+      <c r="C29" s="33" t="inlineStr">
         <is>
           <t>https://arraymed.co.in/product/fresenius-kabi-agilia-sp/</t>
         </is>
@@ -3718,7 +3716,7 @@
       </c>
       <c r="E29" s="13" t="inlineStr">
         <is>
-          <t>ADDED (yellow)</t>
+          <t>ADDED (peach)</t>
         </is>
       </c>
       <c r="F29" s="13" t="inlineStr"/>
@@ -3734,7 +3732,7 @@
           <t>Agilia SP MC (drug-library evidence)</t>
         </is>
       </c>
-      <c r="C30" s="32" t="inlineStr">
+      <c r="C30" s="33" t="inlineStr">
         <is>
           <t>https://arraymed.co.in/product/fresenius-kabi-agilia-spmc/</t>
         </is>
@@ -3746,7 +3744,7 @@
       </c>
       <c r="E30" s="13" t="inlineStr">
         <is>
-          <t>ADDED (yellow)</t>
+          <t>ADDED (peach)</t>
         </is>
       </c>
       <c r="F30" s="13" t="inlineStr"/>
@@ -3762,7 +3760,7 @@
           <t>Agilia SP TIVA (WiFi variant evidence)</t>
         </is>
       </c>
-      <c r="C31" s="32" t="inlineStr">
+      <c r="C31" s="33" t="inlineStr">
         <is>
           <t>https://arraymed.co.in/product/fresenius-kabi-agilia-tiva-pump/</t>
         </is>
@@ -3774,7 +3772,7 @@
       </c>
       <c r="E31" s="13" t="inlineStr">
         <is>
-          <t>ADDED (yellow)</t>
+          <t>ADDED (peach)</t>
         </is>
       </c>
       <c r="F31" s="13" t="inlineStr"/>
@@ -3790,7 +3788,7 @@
           <t>Agilia SP MC / SP MC WiFi data sheet</t>
         </is>
       </c>
-      <c r="C32" s="32" t="inlineStr">
+      <c r="C32" s="33" t="inlineStr">
         <is>
           <t>https://www.fresenius-kabi.com/content/dam/fresenius-kabi/gb/products/product-documents/medtech/agilia-connect-sp/IFT265%20Agilia%20SP%20Connect%20Datasheet.pdf.coredownload.inline.pdf</t>
         </is>
@@ -3822,7 +3820,7 @@
           <t>Segment reporting FY2025 (revenue)</t>
         </is>
       </c>
-      <c r="C33" s="32" t="inlineStr">
+      <c r="C33" s="33" t="inlineStr">
         <is>
           <t>https://report.fresenius.com/2025/annual-report/financial-statements/segment-reporting.html</t>
         </is>
@@ -3854,7 +3852,7 @@
           <t>Annual Report 2025 PDF (p.5, p.117)</t>
         </is>
       </c>
-      <c r="C34" s="32" t="inlineStr">
+      <c r="C34" s="33" t="inlineStr">
         <is>
           <t>https://www.fresenius.com/sites/default/files/2026-03/fresenius_annual_report_2025_0.pdf</t>
         </is>
@@ -3886,7 +3884,7 @@
           <t>India entity financials</t>
         </is>
       </c>
-      <c r="C35" s="32" t="inlineStr">
+      <c r="C35" s="33" t="inlineStr">
         <is>
           <t>https://www.tofler.in/fresenius-kabi-india-private-limited/company/U24231PN1995PTC014017</t>
         </is>
@@ -3918,7 +3916,7 @@
           <t>GB product literature library</t>
         </is>
       </c>
-      <c r="C36" s="32" t="inlineStr">
+      <c r="C36" s="33" t="inlineStr">
         <is>
           <t>https://www.fresenius-kabi.com/gb/healthcare-professional-area/medtech/product-literature-library</t>
         </is>
@@ -3928,7 +3926,7 @@
           <t>Global website (GB HCP area)</t>
         </is>
       </c>
-      <c r="E36" s="24" t="inlineStr">
+      <c r="E36" s="28" t="inlineStr">
         <is>
           <t>DROP</t>
         </is>
@@ -3950,7 +3948,7 @@
           <t>Key2 Declaration of Conformity</t>
         </is>
       </c>
-      <c r="C37" s="32" t="inlineStr">
+      <c r="C37" s="33" t="inlineStr">
         <is>
           <t>https://key2.fresenius-kabi.com/en/regulatory-document/declaration-conformity/mdr/declaration-conformity</t>
         </is>
@@ -3960,7 +3958,7 @@
           <t>Regulatory document (EU)</t>
         </is>
       </c>
-      <c r="E37" s="24" t="inlineStr">
+      <c r="E37" s="28" t="inlineStr">
         <is>
           <t>DROP</t>
         </is>
@@ -4060,65 +4058,65 @@
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" s="28" t="inlineStr">
+      <c r="A1" s="29" t="inlineStr">
         <is>
           <t>Method, assumptions and caveats</t>
         </is>
       </c>
     </row>
     <row r="3" ht="42" customHeight="1">
-      <c r="A3" s="33" t="inlineStr">
+      <c r="A3" s="34" t="inlineStr">
         <is>
           <t>1. Scope: India market, B. Braun and Fresenius Kabi; syringe and volumetric (large-volume) pumps. BD and Baxter skipped per instruction. Checked October 2026.</t>
         </is>
       </c>
     </row>
     <row r="4" ht="42" customHeight="1">
-      <c r="A4" s="33" t="inlineStr">
-        <is>
-          <t>2. Source priority: (1) company India website, including its catalogue tabs and linked brochures; (2) Indian distributor websites, marked yellow; (3) global company pages/data sheets, used only as backup for features and never as proof of India availability.</t>
+      <c r="A4" s="34" t="inlineStr">
+        <is>
+          <t>2. Source priority: (1) company India website, including its catalogue tabs and linked brochures; (2) Indian distributor websites incl. IndiaMart, marked peach; (3) global company pages/data sheets, used only as backup for features and never as proof of India availability.</t>
         </is>
       </c>
     </row>
     <row r="5" ht="42" customHeight="1">
-      <c r="A5" s="33" t="inlineStr">
+      <c r="A5" s="34" t="inlineStr">
         <is>
           <t>3. Visual check: every India page was opened in a real browser and screenshotted (see evidence/ folder). B. Braun catalogue details sit under 'Read more' / 'Overview &amp; Texts' - click there to see drug-library text.</t>
         </is>
       </c>
     </row>
     <row r="6" ht="42" customHeight="1">
-      <c r="A6" s="33" t="inlineStr">
+      <c r="A6" s="34" t="inlineStr">
         <is>
           <t>4. Classification rules applied: an add-on connectivity module (e.g., Data module compactplus) or a separate WiFi variant (e.g., Agilia SP MC vs SP MC WiFi) = 'connectivity optional' = Smart**. A basic RS232 / nurse-call port is NOT counted as connectivity.</t>
         </is>
       </c>
     </row>
     <row r="7" ht="42" customHeight="1">
-      <c r="A7" s="33" t="inlineStr">
+      <c r="A7" s="34" t="inlineStr">
         <is>
           <t>5. Where a product page is silent on the drug library (e.g., FK Agilia SP, SP TIVA), distributor text was used and the evidence column says so.</t>
         </is>
       </c>
     </row>
     <row r="8" ht="42" customHeight="1">
-      <c r="A8" s="33" t="inlineStr">
-        <is>
-          <t>6. LIMITATION: IndiaMart blocks automated access from this environment (HTTP 429), so the IndiaMart links could not be checked. Agilia VP MC WiFi remains unverified for India.</t>
+      <c r="A8" s="34" t="inlineStr">
+        <is>
+          <t>6. LIMITATION: IndiaMart blocks automated access from this environment (HTTP 429). IndiaMart checks were done manually by the project team; Agilia VP MC WiFi is pending that check.</t>
         </is>
       </c>
     </row>
     <row r="9" ht="42" customHeight="1">
-      <c r="A9" s="33" t="inlineStr">
+      <c r="A9" s="34" t="inlineStr">
         <is>
           <t>7. LIMITATION: Revenue for the India entities is shown only as ranges (Tofler/Tracxn); exact MCA figures are paywalled. Neither group reports infusion-pump-only revenue; Hospital Care (B. Braun) and MedTech (Fresenius Kabi) are the closest disclosed proxies.</t>
         </is>
       </c>
     </row>
     <row r="10" ht="42" customHeight="1">
-      <c r="A10" s="33" t="inlineStr">
-        <is>
-          <t>8. Revenue in USD uses EUR/USD 1.148 (implied by sample) - an editable input on the Revenue tab.</t>
+      <c r="A10" s="34" t="inlineStr">
+        <is>
+          <t>8. Revenue in USD uses the latest ECB EUR/USD reference rate 1.1204 (5-Oct-2026) - an editable input on the Revenue tab. Slide shows official (annual report) figures only; India-entity ranges come from aggregators (Tofler/Tracxn) and are kept off the slide. Official India figures would need MCA filings (paid access).</t>
         </is>
       </c>
     </row>

--- a/Infusion_Pumps_India/Infusion_Pump_Classification_India.xlsx
+++ b/Infusion_Pumps_India/Infusion_Pump_Classification_India.xlsx
@@ -15,7 +15,7 @@
   </sheets>
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Product Evidence'!$A$1:$M$20</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'Clean URL Map'!$A$1:$F$38</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'Clean URL Map'!$A$1:$F$40</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -236,7 +236,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="35">
+  <cellXfs count="34">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
@@ -270,9 +270,6 @@
     <xf numFmtId="0" fontId="3" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="3" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
@@ -295,9 +292,6 @@
     <xf numFmtId="0" fontId="7" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="8" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="9" fillId="8" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="164" fontId="10" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
@@ -307,6 +301,9 @@
       <alignment vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="11" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
@@ -861,7 +858,7 @@
       <c r="K6" s="16" t="n"/>
       <c r="L6" s="4" t="inlineStr">
         <is>
-          <t>Pending confirmation of an Indian distributor listing</t>
+          <t>Pending confirmation of an Indian listing (none open)</t>
         </is>
       </c>
     </row>
@@ -944,16 +941,12 @@
           <t>Infusia VP7s (VP7sED3)</t>
         </is>
       </c>
-      <c r="I9" s="19" t="inlineStr">
-        <is>
-          <t>Agilia VP MC WiFi (pending India confirmation)</t>
-        </is>
-      </c>
+      <c r="I9" s="15" t="n"/>
       <c r="J9" s="13" t="inlineStr">
         <is>
           <t>- Add Agilia SP (Smart), Agilia SP MC &amp; SP TIVA (Smart**)
 - Agilia VP (distributor only) -&gt; Volumetric Smart, peach
-- Agilia VP MC WiFi: pending distributor confirmation (keep only if an Indian listing is found)
+- 'Agilia VP MC WiFi' -&gt; India listing (IndiaMart) is base Agilia VP MC -&gt; Volumetric Smart** (peach); Volumetric Connected now blank
 - Infusia SP7s/VP7s &amp; Agilia SP MC WiFi confirmed</t>
         </is>
       </c>
@@ -970,12 +963,12 @@
       </c>
       <c r="F10" s="18" t="n"/>
       <c r="G10" s="17" t="n"/>
-      <c r="H10" s="20" t="inlineStr">
+      <c r="H10" s="19" t="inlineStr">
         <is>
           <t>Agilia VP</t>
         </is>
       </c>
-      <c r="I10" s="18" t="n"/>
+      <c r="I10" s="17" t="n"/>
       <c r="J10" s="17" t="n"/>
     </row>
     <row r="11" ht="30" customHeight="1">
@@ -990,8 +983,12 @@
       </c>
       <c r="F11" s="18" t="n"/>
       <c r="G11" s="17" t="n"/>
-      <c r="H11" s="18" t="n"/>
-      <c r="I11" s="18" t="n"/>
+      <c r="H11" s="19" t="inlineStr">
+        <is>
+          <t>Agilia VP MC**</t>
+        </is>
+      </c>
+      <c r="I11" s="17" t="n"/>
       <c r="J11" s="17" t="n"/>
     </row>
     <row r="12" ht="30" customHeight="1">
@@ -1007,25 +1004,25 @@
       <c r="F12" s="18" t="n"/>
       <c r="G12" s="10" t="n"/>
       <c r="H12" s="18" t="n"/>
-      <c r="I12" s="18" t="n"/>
+      <c r="I12" s="10" t="n"/>
       <c r="J12" s="10" t="n"/>
     </row>
     <row r="14">
-      <c r="A14" s="21" t="inlineStr">
+      <c r="A14" s="20" t="inlineStr">
         <is>
           <t>** Smart** = drug library + connectivity optional (separately sold data module / WiFi variant).  * USD converted at ECB EUR/USD reference rate 1.1204 (5-Oct-2026), latest available; sample slide had used ~1.148.</t>
         </is>
       </c>
     </row>
     <row r="15">
-      <c r="A15" s="21" t="inlineStr">
+      <c r="A15" s="20" t="inlineStr">
         <is>
           <t>BD and Baxter excluded from this pass per instruction. Product-level evidence and URLs: see 'Product Evidence' tab.</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <mergeCells count="15">
+  <mergeCells count="16">
     <mergeCell ref="J9:J12"/>
     <mergeCell ref="D9:D12"/>
     <mergeCell ref="C9:C12"/>
@@ -1033,6 +1030,7 @@
     <mergeCell ref="B9:B12"/>
     <mergeCell ref="G9:G12"/>
     <mergeCell ref="C6:C8"/>
+    <mergeCell ref="I9:I12"/>
     <mergeCell ref="D4:F4"/>
     <mergeCell ref="J4:J5"/>
     <mergeCell ref="G4:I4"/>
@@ -1143,7 +1141,7 @@
           <t>B. Braun</t>
         </is>
       </c>
-      <c r="B2" s="22" t="inlineStr">
+      <c r="B2" s="21" t="inlineStr">
         <is>
           <t>Perfusor compact</t>
         </is>
@@ -1168,12 +1166,12 @@
           <t>Standard</t>
         </is>
       </c>
-      <c r="G2" s="22" t="inlineStr">
+      <c r="G2" s="21" t="inlineStr">
         <is>
           <t>Official India website</t>
         </is>
       </c>
-      <c r="H2" s="23" t="inlineStr">
+      <c r="H2" s="22" t="inlineStr">
         <is>
           <t>https://catalogs.bbraun.co.in/en-IN/p/PRID00000461</t>
         </is>
@@ -1210,7 +1208,7 @@
           <t>B. Braun</t>
         </is>
       </c>
-      <c r="B3" s="22" t="inlineStr">
+      <c r="B3" s="21" t="inlineStr">
         <is>
           <t>Perfusor compact S</t>
         </is>
@@ -1235,12 +1233,12 @@
           <t>Standard</t>
         </is>
       </c>
-      <c r="G3" s="22" t="inlineStr">
+      <c r="G3" s="21" t="inlineStr">
         <is>
           <t>Official India website</t>
         </is>
       </c>
-      <c r="H3" s="23" t="inlineStr">
+      <c r="H3" s="22" t="inlineStr">
         <is>
           <t>https://catalogs.bbraun.co.in/en-IN/p/PRID00000145</t>
         </is>
@@ -1277,7 +1275,7 @@
           <t>B. Braun</t>
         </is>
       </c>
-      <c r="B4" s="22" t="inlineStr">
+      <c r="B4" s="21" t="inlineStr">
         <is>
           <t>Perfusor compactplus</t>
         </is>
@@ -1302,12 +1300,12 @@
           <t>Smart**</t>
         </is>
       </c>
-      <c r="G4" s="22" t="inlineStr">
+      <c r="G4" s="21" t="inlineStr">
         <is>
           <t>Official India website</t>
         </is>
       </c>
-      <c r="H4" s="23" t="inlineStr">
+      <c r="H4" s="22" t="inlineStr">
         <is>
           <t>https://catalogs.bbraun.co.in/en-IN/p/PRID00010216</t>
         </is>
@@ -1340,7 +1338,7 @@
           <t>B. Braun</t>
         </is>
       </c>
-      <c r="B5" s="22" t="inlineStr">
+      <c r="B5" s="21" t="inlineStr">
         <is>
           <t>Perfusor Space</t>
         </is>
@@ -1365,12 +1363,12 @@
           <t>Smart**</t>
         </is>
       </c>
-      <c r="G5" s="22" t="inlineStr">
+      <c r="G5" s="21" t="inlineStr">
         <is>
           <t>Official India website</t>
         </is>
       </c>
-      <c r="H5" s="23" t="inlineStr">
+      <c r="H5" s="22" t="inlineStr">
         <is>
           <t>https://catalogs.bbraun.co.in/en-IN/p/PRID00001226</t>
         </is>
@@ -1407,7 +1405,7 @@
           <t>B. Braun</t>
         </is>
       </c>
-      <c r="B6" s="24" t="inlineStr">
+      <c r="B6" s="23" t="inlineStr">
         <is>
           <t>Spaceplus Perfusor</t>
         </is>
@@ -1432,12 +1430,12 @@
           <t>Excluded - not offered in India</t>
         </is>
       </c>
-      <c r="G6" s="24" t="inlineStr">
+      <c r="G6" s="23" t="inlineStr">
         <is>
           <t>Not offered in India</t>
         </is>
       </c>
-      <c r="H6" s="25" t="inlineStr">
+      <c r="H6" s="24" t="inlineStr">
         <is>
           <t>https://catalogs.bbraun.co.in/en-IN/p/PRID00011858 (returns 'No results')</t>
         </is>
@@ -1474,7 +1472,7 @@
           <t>B. Braun</t>
         </is>
       </c>
-      <c r="B7" s="22" t="inlineStr">
+      <c r="B7" s="21" t="inlineStr">
         <is>
           <t>Infusomat fmS</t>
         </is>
@@ -1499,12 +1497,12 @@
           <t>Standard</t>
         </is>
       </c>
-      <c r="G7" s="22" t="inlineStr">
+      <c r="G7" s="21" t="inlineStr">
         <is>
           <t>Official India website</t>
         </is>
       </c>
-      <c r="H7" s="23" t="inlineStr">
+      <c r="H7" s="22" t="inlineStr">
         <is>
           <t>https://catalogs.bbraun.co.in/en-IN/p/PRID00000618</t>
         </is>
@@ -1537,7 +1535,7 @@
           <t>B. Braun</t>
         </is>
       </c>
-      <c r="B8" s="22" t="inlineStr">
+      <c r="B8" s="21" t="inlineStr">
         <is>
           <t>Infusomat P</t>
         </is>
@@ -1562,12 +1560,12 @@
           <t>Standard</t>
         </is>
       </c>
-      <c r="G8" s="22" t="inlineStr">
+      <c r="G8" s="21" t="inlineStr">
         <is>
           <t>Official India website</t>
         </is>
       </c>
-      <c r="H8" s="23" t="inlineStr">
+      <c r="H8" s="22" t="inlineStr">
         <is>
           <t>https://catalogs.bbraun.co.in/en-IN/p/PRID00000689</t>
         </is>
@@ -1600,7 +1598,7 @@
           <t>B. Braun</t>
         </is>
       </c>
-      <c r="B9" s="22" t="inlineStr">
+      <c r="B9" s="21" t="inlineStr">
         <is>
           <t>Infusomat compactplus</t>
         </is>
@@ -1625,12 +1623,12 @@
           <t>Smart**</t>
         </is>
       </c>
-      <c r="G9" s="22" t="inlineStr">
+      <c r="G9" s="21" t="inlineStr">
         <is>
           <t>Official India website</t>
         </is>
       </c>
-      <c r="H9" s="23" t="inlineStr">
+      <c r="H9" s="22" t="inlineStr">
         <is>
           <t>https://catalogs.bbraun.co.in/en-IN/p/PRID00011042</t>
         </is>
@@ -1663,7 +1661,7 @@
           <t>B. Braun</t>
         </is>
       </c>
-      <c r="B10" s="22" t="inlineStr">
+      <c r="B10" s="21" t="inlineStr">
         <is>
           <t>Infusomat compactplus P</t>
         </is>
@@ -1688,12 +1686,12 @@
           <t>Smart**</t>
         </is>
       </c>
-      <c r="G10" s="22" t="inlineStr">
+      <c r="G10" s="21" t="inlineStr">
         <is>
           <t>Official India website</t>
         </is>
       </c>
-      <c r="H10" s="23" t="inlineStr">
+      <c r="H10" s="22" t="inlineStr">
         <is>
           <t>https://catalogs.bbraun.co.in/en-IN/p/PRID00012086</t>
         </is>
@@ -1730,7 +1728,7 @@
           <t>B. Braun</t>
         </is>
       </c>
-      <c r="B11" s="22" t="inlineStr">
+      <c r="B11" s="21" t="inlineStr">
         <is>
           <t>Infusomat Space P</t>
         </is>
@@ -1755,12 +1753,12 @@
           <t>Smart**</t>
         </is>
       </c>
-      <c r="G11" s="22" t="inlineStr">
+      <c r="G11" s="21" t="inlineStr">
         <is>
           <t>Official India website</t>
         </is>
       </c>
-      <c r="H11" s="23" t="inlineStr">
+      <c r="H11" s="22" t="inlineStr">
         <is>
           <t>https://catalogs.bbraun.co.in/en-IN/p/PRID00001230</t>
         </is>
@@ -1793,7 +1791,7 @@
           <t>B. Braun</t>
         </is>
       </c>
-      <c r="B12" s="22" t="inlineStr">
+      <c r="B12" s="21" t="inlineStr">
         <is>
           <t>Spaceplus Infusomat</t>
         </is>
@@ -1818,12 +1816,12 @@
           <t>Connected</t>
         </is>
       </c>
-      <c r="G12" s="22" t="inlineStr">
+      <c r="G12" s="21" t="inlineStr">
         <is>
           <t>Official India website</t>
         </is>
       </c>
-      <c r="H12" s="23" t="inlineStr">
+      <c r="H12" s="22" t="inlineStr">
         <is>
           <t>https://catalogs.bbraun.co.in/en-IN/p/PRID00011860</t>
         </is>
@@ -1856,7 +1854,7 @@
           <t>Fresenius Kabi</t>
         </is>
       </c>
-      <c r="B13" s="22" t="inlineStr">
+      <c r="B13" s="21" t="inlineStr">
         <is>
           <t>Infusia SP7s (SP7sED3)</t>
         </is>
@@ -1881,12 +1879,12 @@
           <t>Smart</t>
         </is>
       </c>
-      <c r="G13" s="22" t="inlineStr">
+      <c r="G13" s="21" t="inlineStr">
         <is>
           <t>Official India website</t>
         </is>
       </c>
-      <c r="H13" s="23" t="inlineStr">
+      <c r="H13" s="22" t="inlineStr">
         <is>
           <t>https://www.fresenius-kabi.com/in/products/ins/infusion-therapy/infusia-range/infusia-sp7sed3</t>
         </is>
@@ -1923,7 +1921,7 @@
           <t>Fresenius Kabi</t>
         </is>
       </c>
-      <c r="B14" s="22" t="inlineStr">
+      <c r="B14" s="21" t="inlineStr">
         <is>
           <t>Agilia SP</t>
         </is>
@@ -1948,12 +1946,12 @@
           <t>Smart</t>
         </is>
       </c>
-      <c r="G14" s="22" t="inlineStr">
+      <c r="G14" s="21" t="inlineStr">
         <is>
           <t>Official India website</t>
         </is>
       </c>
-      <c r="H14" s="23" t="inlineStr">
+      <c r="H14" s="22" t="inlineStr">
         <is>
           <t>https://www.fresenius-kabi.com/in/products/ins/infusion-therapy/agilia-range/agilia-sp</t>
         </is>
@@ -1990,7 +1988,7 @@
           <t>Fresenius Kabi</t>
         </is>
       </c>
-      <c r="B15" s="22" t="inlineStr">
+      <c r="B15" s="21" t="inlineStr">
         <is>
           <t>Agilia SP MC</t>
         </is>
@@ -2015,12 +2013,12 @@
           <t>Smart**</t>
         </is>
       </c>
-      <c r="G15" s="22" t="inlineStr">
+      <c r="G15" s="21" t="inlineStr">
         <is>
           <t>Official India website</t>
         </is>
       </c>
-      <c r="H15" s="23" t="inlineStr">
+      <c r="H15" s="22" t="inlineStr">
         <is>
           <t>https://www.fresenius-kabi.com/in/products/ins/infusion-therapy/agilia-range/agilia-sp-mc</t>
         </is>
@@ -2053,7 +2051,7 @@
           <t>Fresenius Kabi</t>
         </is>
       </c>
-      <c r="B16" s="22" t="inlineStr">
+      <c r="B16" s="21" t="inlineStr">
         <is>
           <t>Agilia SP MC WiFi</t>
         </is>
@@ -2078,12 +2076,12 @@
           <t>Connected</t>
         </is>
       </c>
-      <c r="G16" s="22" t="inlineStr">
+      <c r="G16" s="21" t="inlineStr">
         <is>
           <t>Official India website</t>
         </is>
       </c>
-      <c r="H16" s="23" t="inlineStr">
+      <c r="H16" s="22" t="inlineStr">
         <is>
           <t>https://www.fresenius-kabi.com/in/products/ins/infusion-therapy/agilia-range/agilia-sp-mc</t>
         </is>
@@ -2120,7 +2118,7 @@
           <t>Fresenius Kabi</t>
         </is>
       </c>
-      <c r="B17" s="22" t="inlineStr">
+      <c r="B17" s="21" t="inlineStr">
         <is>
           <t>Agilia SP TIVA</t>
         </is>
@@ -2145,12 +2143,12 @@
           <t>Smart**</t>
         </is>
       </c>
-      <c r="G17" s="22" t="inlineStr">
+      <c r="G17" s="21" t="inlineStr">
         <is>
           <t>Official India website</t>
         </is>
       </c>
-      <c r="H17" s="23" t="inlineStr">
+      <c r="H17" s="22" t="inlineStr">
         <is>
           <t>https://www.fresenius-kabi.com/in/products/ins/infusion-therapy/agilia-range/agilia-sp-tiva</t>
         </is>
@@ -2187,7 +2185,7 @@
           <t>Fresenius Kabi</t>
         </is>
       </c>
-      <c r="B18" s="22" t="inlineStr">
+      <c r="B18" s="21" t="inlineStr">
         <is>
           <t>Infusia VP7s (VP7sED3)</t>
         </is>
@@ -2212,12 +2210,12 @@
           <t>Smart</t>
         </is>
       </c>
-      <c r="G18" s="22" t="inlineStr">
+      <c r="G18" s="21" t="inlineStr">
         <is>
           <t>Official India website</t>
         </is>
       </c>
-      <c r="H18" s="23" t="inlineStr">
+      <c r="H18" s="22" t="inlineStr">
         <is>
           <t>https://www.fresenius-kabi.com/in/products/ins/infusion-therapy/infusia-range/infusia-vp7sed3</t>
         </is>
@@ -2250,7 +2248,7 @@
           <t>Fresenius Kabi</t>
         </is>
       </c>
-      <c r="B19" s="26" t="inlineStr">
+      <c r="B19" s="25" t="inlineStr">
         <is>
           <t>Agilia VP</t>
         </is>
@@ -2275,12 +2273,12 @@
           <t>Smart</t>
         </is>
       </c>
-      <c r="G19" s="26" t="inlineStr">
+      <c r="G19" s="25" t="inlineStr">
         <is>
           <t>Third-party (India distributor)</t>
         </is>
       </c>
-      <c r="H19" s="27" t="inlineStr">
+      <c r="H19" s="26" t="inlineStr">
         <is>
           <t>https://arraymed.co.in/product/fresenius-kabi-agilia-vp/</t>
         </is>
@@ -2317,9 +2315,9 @@
           <t>Fresenius Kabi</t>
         </is>
       </c>
-      <c r="B20" s="28" t="inlineStr">
-        <is>
-          <t>Agilia VP MC WiFi</t>
+      <c r="B20" s="25" t="inlineStr">
+        <is>
+          <t>Agilia VP MC</t>
         </is>
       </c>
       <c r="C20" s="13" t="inlineStr">
@@ -2329,52 +2327,52 @@
       </c>
       <c r="D20" s="13" t="inlineStr">
         <is>
-          <t>Yes (global) - FK data sheet: 'Up to 19 embedded drug libraries'.</t>
+          <t>Yes - FK data sheet: 'Up to 19 embedded drug libraries'; 'Drug library to be created with Agilia Vigilant Drug'Lib'.</t>
         </is>
       </c>
       <c r="E20" s="13" t="inlineStr">
         <is>
-          <t>Integrated WiFi on WiFi variant (global) - 'Wireless LAN (For Agilia VP MC WiFi only)'.</t>
+          <t>Optional - WiFi only on the separate Agilia VP MC WiFi variant (data sheet: 'Wireless LAN (For Agilia VP MC WiFi only)'). The WiFi variant was not found listed in India.</t>
         </is>
       </c>
       <c r="F20" s="12" t="inlineStr">
         <is>
-          <t>Connected (global only)</t>
-        </is>
-      </c>
-      <c r="G20" s="28" t="inlineStr">
-        <is>
-          <t>Not verified in India</t>
-        </is>
-      </c>
-      <c r="H20" s="28" t="inlineStr">
-        <is>
-          <t>Pending - not on FK India site or Arraymed; IndiaMart search for team check: https://dir.indiamart.com/search.mp?ss=agilia+vp+mc+wifi</t>
+          <t>Smart**</t>
+        </is>
+      </c>
+      <c r="G20" s="25" t="inlineStr">
+        <is>
+          <t>Third-party (India distributor)</t>
+        </is>
+      </c>
+      <c r="H20" s="26" t="inlineStr">
+        <is>
+          <t>https://dir.indiamart.com/search.mp?ss=agilia+vp+mc+wifi (listing: 'Fresenius Kabi Agilia VP MC'; product-page URL to be added)</t>
         </is>
       </c>
       <c r="I20" s="13" t="inlineStr">
         <is>
-          <t>Global data sheet: https://www.fresenius-kabi.com/content/dam/fresenius-kabi/gb/products/product-documents/medtech/agilia-connect-vp/IFT264%20Agilia%20VPMC%20Connect%20Data%20Sheet.pdf.coredownload.inline.pdf</t>
+          <t>FK data sheet p.1-2: https://www.fresenius-kabi.com/content/dam/fresenius-kabi/gb/products/product-documents/medtech/agilia-connect-vp/IFT264%20Agilia%20VPMC%20Connect%20Data%20Sheet.pdf.coredownload.inline.pdf</t>
         </is>
       </c>
       <c r="J20" s="13" t="inlineStr">
         <is>
-          <t>Connected (Indian distributors' websites)</t>
+          <t>Connected - 'Agilia VP MC WiFi' (Indian distributors' websites)</t>
         </is>
       </c>
       <c r="K20" s="13" t="inlineStr">
         <is>
-          <t>PENDING team confirmation of IndiaMart/distributor listing; remove if none</t>
+          <t>RECLASSIFY: India listing is base Agilia VP MC -&gt; Volumetric-Smart**; WiFi variant not listed in India -&gt; FK Volumetric-Connected now blank</t>
         </is>
       </c>
       <c r="L20" s="13" t="inlineStr">
         <is>
-          <t>IndiaMart blocks automated access (HTTP 429), so IndiaMart could not be checked. Manual check needed.</t>
+          <t>IndiaMart listing verified manually by project team (Oct-2026 screenshot); no price shown; seller not captured. Search for 'agilia vp mc wifi' returned no WiFi-variant listing.</t>
         </is>
       </c>
       <c r="M20" s="13" t="inlineStr">
         <is>
-          <t>FK_IN_Agilia_range.jpg (absence)</t>
+          <t>IndiaMart_search_Agilia_VP_MC_team_check.jpg</t>
         </is>
       </c>
     </row>
@@ -2399,6 +2397,7 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H17" r:id="rId16"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H18" r:id="rId17"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H19" r:id="rId18"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H20" r:id="rId19"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -2427,7 +2426,7 @@
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" s="29" t="inlineStr">
+      <c r="A1" s="27" t="inlineStr">
         <is>
           <t>Revenue cross-check (FY2025)</t>
         </is>
@@ -2439,7 +2438,7 @@
           <t>EUR/USD rate (input)</t>
         </is>
       </c>
-      <c r="B2" s="30" t="n">
+      <c r="B2" s="28" t="n">
         <v>1.1204</v>
       </c>
       <c r="C2" s="2" t="inlineStr">
@@ -2521,10 +2520,10 @@
           <t>FY2025 (Dec-25)</t>
         </is>
       </c>
-      <c r="D5" s="31" t="n">
+      <c r="D5" s="29" t="n">
         <v>9396</v>
       </c>
-      <c r="E5" s="32">
+      <c r="E5" s="30">
         <f>IF(D5="","n/a",D5*$B$2/1000)</f>
         <v/>
       </c>
@@ -2570,10 +2569,10 @@
           <t>FY2025</t>
         </is>
       </c>
-      <c r="D6" s="31" t="n">
+      <c r="D6" s="29" t="n">
         <v>5090.8</v>
       </c>
-      <c r="E6" s="32">
+      <c r="E6" s="30">
         <f>IF(D6="","n/a",D6*$B$2/1000)</f>
         <v/>
       </c>
@@ -2619,8 +2618,8 @@
           <t>FY2025 (Mar-25)</t>
         </is>
       </c>
-      <c r="D7" s="31" t="n"/>
-      <c r="E7" s="32">
+      <c r="D7" s="29" t="n"/>
+      <c r="E7" s="30">
         <f>IF(D7="","n/a",D7*$B$2/1000)</f>
         <v/>
       </c>
@@ -2666,10 +2665,10 @@
           <t>FY2025 (Dec-25)</t>
         </is>
       </c>
-      <c r="D8" s="31" t="n">
+      <c r="D8" s="29" t="n">
         <v>8612</v>
       </c>
-      <c r="E8" s="32">
+      <c r="E8" s="30">
         <f>IF(D8="","n/a",D8*$B$2/1000)</f>
         <v/>
       </c>
@@ -2715,10 +2714,10 @@
           <t>FY2025</t>
         </is>
       </c>
-      <c r="D9" s="31" t="n">
+      <c r="D9" s="29" t="n">
         <v>1610</v>
       </c>
-      <c r="E9" s="32">
+      <c r="E9" s="30">
         <f>IF(D9="","n/a",D9*$B$2/1000)</f>
         <v/>
       </c>
@@ -2764,8 +2763,8 @@
           <t>FY2025 (Mar-25)</t>
         </is>
       </c>
-      <c r="D10" s="31" t="n"/>
-      <c r="E10" s="32">
+      <c r="D10" s="29" t="n"/>
+      <c r="E10" s="30">
         <f>IF(D10="","n/a",D10*$B$2/1000)</f>
         <v/>
       </c>
@@ -2814,7 +2813,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F38"/>
+  <dimension ref="A1:F40"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -2868,12 +2867,12 @@
           <t>India catalogue - automated infusion systems (master list)</t>
         </is>
       </c>
-      <c r="C2" s="33" t="inlineStr">
+      <c r="C2" s="31" t="inlineStr">
         <is>
           <t>https://catalogs.bbraun.co.in/en-IN/c/PRODUCTS0000000529/automated-infusion-systems</t>
         </is>
       </c>
-      <c r="D2" s="22" t="inlineStr">
+      <c r="D2" s="21" t="inlineStr">
         <is>
           <t>Official India website</t>
         </is>
@@ -2900,12 +2899,12 @@
           <t>Perfusor compact</t>
         </is>
       </c>
-      <c r="C3" s="33" t="inlineStr">
+      <c r="C3" s="31" t="inlineStr">
         <is>
           <t>https://catalogs.bbraun.co.in/en-IN/p/PRID00000461</t>
         </is>
       </c>
-      <c r="D3" s="22" t="inlineStr">
+      <c r="D3" s="21" t="inlineStr">
         <is>
           <t>Official India website</t>
         </is>
@@ -2932,12 +2931,12 @@
           <t>Perfusor compact S</t>
         </is>
       </c>
-      <c r="C4" s="33" t="inlineStr">
+      <c r="C4" s="31" t="inlineStr">
         <is>
           <t>https://catalogs.bbraun.co.in/en-IN/p/PRID00000145</t>
         </is>
       </c>
-      <c r="D4" s="22" t="inlineStr">
+      <c r="D4" s="21" t="inlineStr">
         <is>
           <t>Official India website</t>
         </is>
@@ -2964,12 +2963,12 @@
           <t>Perfusor compactplus</t>
         </is>
       </c>
-      <c r="C5" s="33" t="inlineStr">
+      <c r="C5" s="31" t="inlineStr">
         <is>
           <t>https://catalogs.bbraun.co.in/en-IN/p/PRID00010216</t>
         </is>
       </c>
-      <c r="D5" s="22" t="inlineStr">
+      <c r="D5" s="21" t="inlineStr">
         <is>
           <t>Official India website</t>
         </is>
@@ -2996,12 +2995,12 @@
           <t>Data module compactplus (connectivity add-on)</t>
         </is>
       </c>
-      <c r="C6" s="33" t="inlineStr">
+      <c r="C6" s="31" t="inlineStr">
         <is>
           <t>https://catalogs.bbraun.co.in/en-IN/p/PRID00011150</t>
         </is>
       </c>
-      <c r="D6" s="22" t="inlineStr">
+      <c r="D6" s="21" t="inlineStr">
         <is>
           <t>Official India website</t>
         </is>
@@ -3028,7 +3027,7 @@
           <t>compactplus brochure (p.5 data module, p.6 DoseGuard)</t>
         </is>
       </c>
-      <c r="C7" s="33" t="inlineStr">
+      <c r="C7" s="31" t="inlineStr">
         <is>
           <t>https://ecatalog.bbraun.com/eDoc/QlBSMDAwMDAwMDAwMDAwMDAwMTAwMDE4NTA5OTAwMDAw?openInline=true</t>
         </is>
@@ -3056,12 +3055,12 @@
           <t>Perfusor Space</t>
         </is>
       </c>
-      <c r="C8" s="33" t="inlineStr">
+      <c r="C8" s="31" t="inlineStr">
         <is>
           <t>https://catalogs.bbraun.co.in/en-IN/p/PRID00001226</t>
         </is>
       </c>
-      <c r="D8" s="22" t="inlineStr">
+      <c r="D8" s="21" t="inlineStr">
         <is>
           <t>Official India website</t>
         </is>
@@ -3088,12 +3087,12 @@
           <t>Infusomat fmS</t>
         </is>
       </c>
-      <c r="C9" s="33" t="inlineStr">
+      <c r="C9" s="31" t="inlineStr">
         <is>
           <t>https://catalogs.bbraun.co.in/en-IN/p/PRID00000618</t>
         </is>
       </c>
-      <c r="D9" s="22" t="inlineStr">
+      <c r="D9" s="21" t="inlineStr">
         <is>
           <t>Official India website</t>
         </is>
@@ -3120,12 +3119,12 @@
           <t>Infusomat P</t>
         </is>
       </c>
-      <c r="C10" s="33" t="inlineStr">
+      <c r="C10" s="31" t="inlineStr">
         <is>
           <t>https://catalogs.bbraun.co.in/en-IN/p/PRID00000689</t>
         </is>
       </c>
-      <c r="D10" s="22" t="inlineStr">
+      <c r="D10" s="21" t="inlineStr">
         <is>
           <t>Official India website</t>
         </is>
@@ -3152,12 +3151,12 @@
           <t>Infusomat compactplus</t>
         </is>
       </c>
-      <c r="C11" s="33" t="inlineStr">
+      <c r="C11" s="31" t="inlineStr">
         <is>
           <t>https://catalogs.bbraun.co.in/en-IN/p/PRID00011042</t>
         </is>
       </c>
-      <c r="D11" s="22" t="inlineStr">
+      <c r="D11" s="21" t="inlineStr">
         <is>
           <t>Official India website</t>
         </is>
@@ -3184,12 +3183,12 @@
           <t>Infusomat compactplus P</t>
         </is>
       </c>
-      <c r="C12" s="33" t="inlineStr">
+      <c r="C12" s="31" t="inlineStr">
         <is>
           <t>https://catalogs.bbraun.co.in/en-IN/p/PRID00012086</t>
         </is>
       </c>
-      <c r="D12" s="22" t="inlineStr">
+      <c r="D12" s="21" t="inlineStr">
         <is>
           <t>Official India website</t>
         </is>
@@ -3212,12 +3211,12 @@
           <t>Infusomat Space P</t>
         </is>
       </c>
-      <c r="C13" s="33" t="inlineStr">
+      <c r="C13" s="31" t="inlineStr">
         <is>
           <t>https://catalogs.bbraun.co.in/en-IN/p/PRID00001230</t>
         </is>
       </c>
-      <c r="D13" s="22" t="inlineStr">
+      <c r="D13" s="21" t="inlineStr">
         <is>
           <t>Official India website</t>
         </is>
@@ -3240,12 +3239,12 @@
           <t>Spaceplus Infusomat</t>
         </is>
       </c>
-      <c r="C14" s="33" t="inlineStr">
+      <c r="C14" s="31" t="inlineStr">
         <is>
           <t>https://catalogs.bbraun.co.in/en-IN/p/PRID00011860</t>
         </is>
       </c>
-      <c r="D14" s="22" t="inlineStr">
+      <c r="D14" s="21" t="inlineStr">
         <is>
           <t>Official India website</t>
         </is>
@@ -3272,7 +3271,7 @@
           <t>Annual Report 2025 (revenue)</t>
         </is>
       </c>
-      <c r="C15" s="33" t="inlineStr">
+      <c r="C15" s="31" t="inlineStr">
         <is>
           <t>https://www.bbraun.com/en/about-us/company/facts-and-figures/annual-report.html</t>
         </is>
@@ -3304,7 +3303,7 @@
           <t>Annual Report 2025 PDF (p.8, p.43)</t>
         </is>
       </c>
-      <c r="C16" s="33" t="inlineStr">
+      <c r="C16" s="31" t="inlineStr">
         <is>
           <t>https://www.bbraun.com/content/dam/b-braun/master/website-6/en/04_about-us/0401_company/facts-and-figures/2025_B_Braun_Annual_Report.pdf</t>
         </is>
@@ -3336,7 +3335,7 @@
           <t>India entity financials</t>
         </is>
       </c>
-      <c r="C17" s="33" t="inlineStr">
+      <c r="C17" s="31" t="inlineStr">
         <is>
           <t>https://www.tofler.in/b-braun-medical-india-private-limited/company/U33112MH1984PTC214514</t>
         </is>
@@ -3368,7 +3367,7 @@
           <t>compactplus system (global page)</t>
         </is>
       </c>
-      <c r="C18" s="33" t="inlineStr">
+      <c r="C18" s="31" t="inlineStr">
         <is>
           <t>https://www.bbraun.com/en/products-and-solutions/therapies/infusion-therapy/automated-infusion-systems/compactplus-system.html</t>
         </is>
@@ -3378,7 +3377,7 @@
           <t>Global website</t>
         </is>
       </c>
-      <c r="E18" s="28" t="inlineStr">
+      <c r="E18" s="32" t="inlineStr">
         <is>
           <t>DROP</t>
         </is>
@@ -3400,7 +3399,7 @@
           <t>Spaceplus Perfusor (global catalogue)</t>
         </is>
       </c>
-      <c r="C19" s="33" t="inlineStr">
+      <c r="C19" s="31" t="inlineStr">
         <is>
           <t>https://catalogs.bbraun.com/en-01/p/PRID00011858/spaceplus-perfusor</t>
         </is>
@@ -3410,7 +3409,7 @@
           <t>Global website</t>
         </is>
       </c>
-      <c r="E19" s="28" t="inlineStr">
+      <c r="E19" s="32" t="inlineStr">
         <is>
           <t>DROP</t>
         </is>
@@ -3432,12 +3431,12 @@
           <t>India - Infusion Therapy (navigation)</t>
         </is>
       </c>
-      <c r="C20" s="33" t="inlineStr">
+      <c r="C20" s="31" t="inlineStr">
         <is>
           <t>https://www.fresenius-kabi.com/in/products/ins/infusion-therapy</t>
         </is>
       </c>
-      <c r="D20" s="22" t="inlineStr">
+      <c r="D20" s="21" t="inlineStr">
         <is>
           <t>Official India website</t>
         </is>
@@ -3464,12 +3463,12 @@
           <t>India - Agilia range (lists SP, SP MC, SP TIVA only)</t>
         </is>
       </c>
-      <c r="C21" s="33" t="inlineStr">
+      <c r="C21" s="31" t="inlineStr">
         <is>
           <t>https://www.fresenius-kabi.com/in/products/ins/infusion-therapy/agilia-range</t>
         </is>
       </c>
-      <c r="D21" s="22" t="inlineStr">
+      <c r="D21" s="21" t="inlineStr">
         <is>
           <t>Official India website</t>
         </is>
@@ -3496,12 +3495,12 @@
           <t>India - Infusia range</t>
         </is>
       </c>
-      <c r="C22" s="33" t="inlineStr">
+      <c r="C22" s="31" t="inlineStr">
         <is>
           <t>https://www.fresenius-kabi.com/in/products/ins/infusion-therapy/infusia-range</t>
         </is>
       </c>
-      <c r="D22" s="22" t="inlineStr">
+      <c r="D22" s="21" t="inlineStr">
         <is>
           <t>Official India website</t>
         </is>
@@ -3524,12 +3523,12 @@
           <t>Infusia SP7s</t>
         </is>
       </c>
-      <c r="C23" s="33" t="inlineStr">
+      <c r="C23" s="31" t="inlineStr">
         <is>
           <t>https://www.fresenius-kabi.com/in/products/ins/infusion-therapy/infusia-range/infusia-sp7sed3</t>
         </is>
       </c>
-      <c r="D23" s="22" t="inlineStr">
+      <c r="D23" s="21" t="inlineStr">
         <is>
           <t>Official India website</t>
         </is>
@@ -3556,12 +3555,12 @@
           <t>Infusia VP7s</t>
         </is>
       </c>
-      <c r="C24" s="33" t="inlineStr">
+      <c r="C24" s="31" t="inlineStr">
         <is>
           <t>https://www.fresenius-kabi.com/in/products/ins/infusion-therapy/infusia-range/infusia-vp7sed3</t>
         </is>
       </c>
-      <c r="D24" s="22" t="inlineStr">
+      <c r="D24" s="21" t="inlineStr">
         <is>
           <t>Official India website</t>
         </is>
@@ -3584,12 +3583,12 @@
           <t>Agilia SP</t>
         </is>
       </c>
-      <c r="C25" s="33" t="inlineStr">
+      <c r="C25" s="31" t="inlineStr">
         <is>
           <t>https://www.fresenius-kabi.com/in/products/ins/infusion-therapy/agilia-range/agilia-sp</t>
         </is>
       </c>
-      <c r="D25" s="22" t="inlineStr">
+      <c r="D25" s="21" t="inlineStr">
         <is>
           <t>Official India website</t>
         </is>
@@ -3612,12 +3611,12 @@
           <t>Agilia SP MC / SP MC WiFi</t>
         </is>
       </c>
-      <c r="C26" s="33" t="inlineStr">
+      <c r="C26" s="31" t="inlineStr">
         <is>
           <t>https://www.fresenius-kabi.com/in/products/ins/infusion-therapy/agilia-range/agilia-sp-mc</t>
         </is>
       </c>
-      <c r="D26" s="22" t="inlineStr">
+      <c r="D26" s="21" t="inlineStr">
         <is>
           <t>Official India website</t>
         </is>
@@ -3644,12 +3643,12 @@
           <t>Agilia SP TIVA</t>
         </is>
       </c>
-      <c r="C27" s="33" t="inlineStr">
+      <c r="C27" s="31" t="inlineStr">
         <is>
           <t>https://www.fresenius-kabi.com/in/products/ins/infusion-therapy/agilia-range/agilia-sp-tiva</t>
         </is>
       </c>
-      <c r="D27" s="22" t="inlineStr">
+      <c r="D27" s="21" t="inlineStr">
         <is>
           <t>Official India website</t>
         </is>
@@ -3672,12 +3671,12 @@
           <t>Agilia VP (distributor)</t>
         </is>
       </c>
-      <c r="C28" s="33" t="inlineStr">
+      <c r="C28" s="31" t="inlineStr">
         <is>
           <t>https://arraymed.co.in/product/fresenius-kabi-agilia-vp/</t>
         </is>
       </c>
-      <c r="D28" s="26" t="inlineStr">
+      <c r="D28" s="25" t="inlineStr">
         <is>
           <t>Third-party (India distributor)</t>
         </is>
@@ -3704,12 +3703,12 @@
           <t>Agilia SP (drug-library evidence)</t>
         </is>
       </c>
-      <c r="C29" s="33" t="inlineStr">
+      <c r="C29" s="31" t="inlineStr">
         <is>
           <t>https://arraymed.co.in/product/fresenius-kabi-agilia-sp/</t>
         </is>
       </c>
-      <c r="D29" s="26" t="inlineStr">
+      <c r="D29" s="25" t="inlineStr">
         <is>
           <t>Third-party (India distributor)</t>
         </is>
@@ -3732,12 +3731,12 @@
           <t>Agilia SP MC (drug-library evidence)</t>
         </is>
       </c>
-      <c r="C30" s="33" t="inlineStr">
+      <c r="C30" s="31" t="inlineStr">
         <is>
           <t>https://arraymed.co.in/product/fresenius-kabi-agilia-spmc/</t>
         </is>
       </c>
-      <c r="D30" s="26" t="inlineStr">
+      <c r="D30" s="25" t="inlineStr">
         <is>
           <t>Third-party (India distributor)</t>
         </is>
@@ -3760,12 +3759,12 @@
           <t>Agilia SP TIVA (WiFi variant evidence)</t>
         </is>
       </c>
-      <c r="C31" s="33" t="inlineStr">
+      <c r="C31" s="31" t="inlineStr">
         <is>
           <t>https://arraymed.co.in/product/fresenius-kabi-agilia-tiva-pump/</t>
         </is>
       </c>
-      <c r="D31" s="26" t="inlineStr">
+      <c r="D31" s="25" t="inlineStr">
         <is>
           <t>Third-party (India distributor)</t>
         </is>
@@ -3788,7 +3787,7 @@
           <t>Agilia SP MC / SP MC WiFi data sheet</t>
         </is>
       </c>
-      <c r="C32" s="33" t="inlineStr">
+      <c r="C32" s="31" t="inlineStr">
         <is>
           <t>https://www.fresenius-kabi.com/content/dam/fresenius-kabi/gb/products/product-documents/medtech/agilia-connect-sp/IFT265%20Agilia%20SP%20Connect%20Datasheet.pdf.coredownload.inline.pdf</t>
         </is>
@@ -3820,7 +3819,7 @@
           <t>Segment reporting FY2025 (revenue)</t>
         </is>
       </c>
-      <c r="C33" s="33" t="inlineStr">
+      <c r="C33" s="31" t="inlineStr">
         <is>
           <t>https://report.fresenius.com/2025/annual-report/financial-statements/segment-reporting.html</t>
         </is>
@@ -3852,7 +3851,7 @@
           <t>Annual Report 2025 PDF (p.5, p.117)</t>
         </is>
       </c>
-      <c r="C34" s="33" t="inlineStr">
+      <c r="C34" s="31" t="inlineStr">
         <is>
           <t>https://www.fresenius.com/sites/default/files/2026-03/fresenius_annual_report_2025_0.pdf</t>
         </is>
@@ -3884,7 +3883,7 @@
           <t>India entity financials</t>
         </is>
       </c>
-      <c r="C35" s="33" t="inlineStr">
+      <c r="C35" s="31" t="inlineStr">
         <is>
           <t>https://www.tofler.in/fresenius-kabi-india-private-limited/company/U24231PN1995PTC014017</t>
         </is>
@@ -3916,7 +3915,7 @@
           <t>GB product literature library</t>
         </is>
       </c>
-      <c r="C36" s="33" t="inlineStr">
+      <c r="C36" s="31" t="inlineStr">
         <is>
           <t>https://www.fresenius-kabi.com/gb/healthcare-professional-area/medtech/product-literature-library</t>
         </is>
@@ -3926,7 +3925,7 @@
           <t>Global website (GB HCP area)</t>
         </is>
       </c>
-      <c r="E36" s="28" t="inlineStr">
+      <c r="E36" s="32" t="inlineStr">
         <is>
           <t>DROP</t>
         </is>
@@ -3948,7 +3947,7 @@
           <t>Key2 Declaration of Conformity</t>
         </is>
       </c>
-      <c r="C37" s="33" t="inlineStr">
+      <c r="C37" s="31" t="inlineStr">
         <is>
           <t>https://key2.fresenius-kabi.com/en/regulatory-document/declaration-conformity/mdr/declaration-conformity</t>
         </is>
@@ -3958,7 +3957,7 @@
           <t>Regulatory document (EU)</t>
         </is>
       </c>
-      <c r="E37" s="28" t="inlineStr">
+      <c r="E37" s="32" t="inlineStr">
         <is>
           <t>DROP</t>
         </is>
@@ -3972,37 +3971,101 @@
     <row r="38">
       <c r="A38" s="13" t="inlineStr">
         <is>
+          <t>Fresenius Kabi</t>
+        </is>
+      </c>
+      <c r="B38" s="13" t="inlineStr">
+        <is>
+          <t>Agilia VP MC (IndiaMart search; team-verified listing)</t>
+        </is>
+      </c>
+      <c r="C38" s="31" t="inlineStr">
+        <is>
+          <t>https://dir.indiamart.com/search.mp?ss=agilia+vp+mc+wifi</t>
+        </is>
+      </c>
+      <c r="D38" s="25" t="inlineStr">
+        <is>
+          <t>Third-party (India distributor)</t>
+        </is>
+      </c>
+      <c r="E38" s="13" t="inlineStr">
+        <is>
+          <t>ADDED (peach)</t>
+        </is>
+      </c>
+      <c r="F38" s="13" t="inlineStr">
+        <is>
+          <t>Replace with the product-page URL of the 'Fresenius Kabi Agilia VP MC' listing</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" s="13" t="inlineStr">
+        <is>
+          <t>Fresenius Kabi</t>
+        </is>
+      </c>
+      <c r="B39" s="13" t="inlineStr">
+        <is>
+          <t>Agilia VP MC / VP MC WiFi data sheet</t>
+        </is>
+      </c>
+      <c r="C39" s="31" t="inlineStr">
+        <is>
+          <t>https://www.fresenius-kabi.com/content/dam/fresenius-kabi/gb/products/product-documents/medtech/agilia-connect-vp/IFT264%20Agilia%20VPMC%20Connect%20Data%20Sheet.pdf.coredownload.inline.pdf</t>
+        </is>
+      </c>
+      <c r="D39" s="13" t="inlineStr">
+        <is>
+          <t>Company brochure (global)</t>
+        </is>
+      </c>
+      <c r="E39" s="13" t="inlineStr">
+        <is>
+          <t>ADDED (backup)</t>
+        </is>
+      </c>
+      <c r="F39" s="13" t="inlineStr">
+        <is>
+          <t>'Wireless LAN (For Agilia VP MC WiFi only)'; 19 drug libraries</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" s="13" t="inlineStr">
+        <is>
           <t>BD / Baxter</t>
         </is>
       </c>
-      <c r="B38" s="13" t="inlineStr">
+      <c r="B40" s="13" t="inlineStr">
         <is>
           <t>All BD and Baxter URLs</t>
         </is>
       </c>
-      <c r="C38" s="13" t="inlineStr">
+      <c r="C40" s="13" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="D38" s="13" t="inlineStr">
+      <c r="D40" s="13" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="E38" s="13" t="inlineStr">
+      <c r="E40" s="13" t="inlineStr">
         <is>
           <t>OUT OF SCOPE</t>
         </is>
       </c>
-      <c r="F38" s="13" t="inlineStr">
+      <c r="F40" s="13" t="inlineStr">
         <is>
           <t>Skipped per instruction</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:F38"/>
+  <autoFilter ref="A1:F40"/>
   <hyperlinks>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C2" r:id="rId1"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C3" r:id="rId2"/>
@@ -4040,6 +4103,8 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C35" r:id="rId34"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C36" r:id="rId35"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C37" r:id="rId36"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C38" r:id="rId37"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C39" r:id="rId38"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -4058,63 +4123,63 @@
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" s="29" t="inlineStr">
+      <c r="A1" s="27" t="inlineStr">
         <is>
           <t>Method, assumptions and caveats</t>
         </is>
       </c>
     </row>
     <row r="3" ht="42" customHeight="1">
-      <c r="A3" s="34" t="inlineStr">
+      <c r="A3" s="33" t="inlineStr">
         <is>
           <t>1. Scope: India market, B. Braun and Fresenius Kabi; syringe and volumetric (large-volume) pumps. BD and Baxter skipped per instruction. Checked October 2026.</t>
         </is>
       </c>
     </row>
     <row r="4" ht="42" customHeight="1">
-      <c r="A4" s="34" t="inlineStr">
+      <c r="A4" s="33" t="inlineStr">
         <is>
           <t>2. Source priority: (1) company India website, including its catalogue tabs and linked brochures; (2) Indian distributor websites incl. IndiaMart, marked peach; (3) global company pages/data sheets, used only as backup for features and never as proof of India availability.</t>
         </is>
       </c>
     </row>
     <row r="5" ht="42" customHeight="1">
-      <c r="A5" s="34" t="inlineStr">
+      <c r="A5" s="33" t="inlineStr">
         <is>
           <t>3. Visual check: every India page was opened in a real browser and screenshotted (see evidence/ folder). B. Braun catalogue details sit under 'Read more' / 'Overview &amp; Texts' - click there to see drug-library text.</t>
         </is>
       </c>
     </row>
     <row r="6" ht="42" customHeight="1">
-      <c r="A6" s="34" t="inlineStr">
+      <c r="A6" s="33" t="inlineStr">
         <is>
           <t>4. Classification rules applied: an add-on connectivity module (e.g., Data module compactplus) or a separate WiFi variant (e.g., Agilia SP MC vs SP MC WiFi) = 'connectivity optional' = Smart**. A basic RS232 / nurse-call port is NOT counted as connectivity.</t>
         </is>
       </c>
     </row>
     <row r="7" ht="42" customHeight="1">
-      <c r="A7" s="34" t="inlineStr">
+      <c r="A7" s="33" t="inlineStr">
         <is>
           <t>5. Where a product page is silent on the drug library (e.g., FK Agilia SP, SP TIVA), distributor text was used and the evidence column says so.</t>
         </is>
       </c>
     </row>
     <row r="8" ht="42" customHeight="1">
-      <c r="A8" s="34" t="inlineStr">
-        <is>
-          <t>6. LIMITATION: IndiaMart blocks automated access from this environment (HTTP 429). IndiaMart checks were done manually by the project team; Agilia VP MC WiFi is pending that check.</t>
+      <c r="A8" s="33" t="inlineStr">
+        <is>
+          <t>6. LIMITATION: IndiaMart blocks automated access from this environment (HTTP 429). IndiaMart checks were done manually by the project team (screenshot in evidence/).</t>
         </is>
       </c>
     </row>
     <row r="9" ht="42" customHeight="1">
-      <c r="A9" s="34" t="inlineStr">
+      <c r="A9" s="33" t="inlineStr">
         <is>
           <t>7. LIMITATION: Revenue for the India entities is shown only as ranges (Tofler/Tracxn); exact MCA figures are paywalled. Neither group reports infusion-pump-only revenue; Hospital Care (B. Braun) and MedTech (Fresenius Kabi) are the closest disclosed proxies.</t>
         </is>
       </c>
     </row>
     <row r="10" ht="42" customHeight="1">
-      <c r="A10" s="34" t="inlineStr">
+      <c r="A10" s="33" t="inlineStr">
         <is>
           <t>8. Revenue in USD uses the latest ECB EUR/USD reference rate 1.1204 (5-Oct-2026) - an editable input on the Revenue tab. Slide shows official (annual report) figures only; India-entity ranges come from aggregators (Tofler/Tracxn) and are kept off the slide. Official India figures would need MCA filings (paid access).</t>
         </is>

--- a/Infusion_Pumps_India/Infusion_Pump_Classification_India.xlsx
+++ b/Infusion_Pumps_India/Infusion_Pump_Classification_India.xlsx
@@ -2347,7 +2347,7 @@
       </c>
       <c r="H20" s="26" t="inlineStr">
         <is>
-          <t>https://dir.indiamart.com/search.mp?ss=agilia+vp+mc+wifi (listing: 'Fresenius Kabi Agilia VP MC'; product-page URL to be added)</t>
+          <t>https://dir.indiamart.com/search.mp?ss=agilia+vp+mc+wifi&amp;cq=New-Delhi (listing: 'Fresenius Kabi Agilia VP MC'; product-page URL to be added)</t>
         </is>
       </c>
       <c r="I20" s="13" t="inlineStr">
@@ -3981,7 +3981,7 @@
       </c>
       <c r="C38" s="31" t="inlineStr">
         <is>
-          <t>https://dir.indiamart.com/search.mp?ss=agilia+vp+mc+wifi</t>
+          <t>https://dir.indiamart.com/search.mp?ss=agilia+vp+mc+wifi&amp;cq=New-Delhi</t>
         </is>
       </c>
       <c r="D38" s="25" t="inlineStr">

--- a/Infusion_Pumps_India/Infusion_Pump_Classification_India.xlsx
+++ b/Infusion_Pumps_India/Infusion_Pump_Classification_India.xlsx
@@ -674,7 +674,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L15"/>
+  <dimension ref="A1:L14"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -944,7 +944,8 @@
       <c r="I9" s="15" t="n"/>
       <c r="J9" s="13" t="inlineStr">
         <is>
-          <t>- Add Agilia SP (Smart), Agilia SP MC &amp; SP TIVA (Smart**)
+          <t>- Add Agilia SP (Smart), Agilia SP MC (Smart**)
+- Agilia SP TIVA excluded: specialty TCI/anaesthesia pump
 - Agilia VP (distributor only) -&gt; Volumetric Smart, peach
 - 'Agilia VP MC WiFi' -&gt; India listing (IndiaMart) is base Agilia VP MC -&gt; Volumetric Smart** (peach); Volumetric Connected now blank
 - Infusia SP7s/VP7s &amp; Agilia SP MC WiFi confirmed</t>
@@ -972,71 +973,55 @@
       <c r="J10" s="17" t="n"/>
     </row>
     <row r="11" ht="30" customHeight="1">
-      <c r="A11" s="17" t="n"/>
-      <c r="B11" s="17" t="n"/>
-      <c r="C11" s="17" t="n"/>
-      <c r="D11" s="17" t="n"/>
+      <c r="A11" s="10" t="n"/>
+      <c r="B11" s="10" t="n"/>
+      <c r="C11" s="10" t="n"/>
+      <c r="D11" s="10" t="n"/>
       <c r="E11" s="14" t="inlineStr">
         <is>
           <t>Agilia SP MC**</t>
         </is>
       </c>
       <c r="F11" s="18" t="n"/>
-      <c r="G11" s="17" t="n"/>
+      <c r="G11" s="10" t="n"/>
       <c r="H11" s="19" t="inlineStr">
         <is>
           <t>Agilia VP MC**</t>
         </is>
       </c>
-      <c r="I11" s="17" t="n"/>
-      <c r="J11" s="17" t="n"/>
-    </row>
-    <row r="12" ht="30" customHeight="1">
-      <c r="A12" s="10" t="n"/>
-      <c r="B12" s="10" t="n"/>
-      <c r="C12" s="10" t="n"/>
-      <c r="D12" s="10" t="n"/>
-      <c r="E12" s="14" t="inlineStr">
-        <is>
-          <t>Agilia SP TIVA**</t>
-        </is>
-      </c>
-      <c r="F12" s="18" t="n"/>
-      <c r="G12" s="10" t="n"/>
-      <c r="H12" s="18" t="n"/>
-      <c r="I12" s="10" t="n"/>
-      <c r="J12" s="10" t="n"/>
+      <c r="I11" s="10" t="n"/>
+      <c r="J11" s="10" t="n"/>
+    </row>
+    <row r="13">
+      <c r="A13" s="20" t="inlineStr">
+        <is>
+          <t>** Smart** = drug library + connectivity optional (separately sold data module / WiFi variant).  * USD converted at ECB EUR/USD reference rate 1.1204 (5-Oct-2026), latest available; sample slide had used ~1.148.</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" s="20" t="inlineStr">
         <is>
-          <t>** Smart** = drug library + connectivity optional (separately sold data module / WiFi variant).  * USD converted at ECB EUR/USD reference rate 1.1204 (5-Oct-2026), latest available; sample slide had used ~1.148.</t>
-        </is>
-      </c>
-    </row>
-    <row r="15">
-      <c r="A15" s="20" t="inlineStr">
-        <is>
           <t>BD and Baxter excluded from this pass per instruction. Product-level evidence and URLs: see 'Product Evidence' tab.</t>
         </is>
       </c>
     </row>
   </sheetData>
   <mergeCells count="16">
-    <mergeCell ref="J9:J12"/>
-    <mergeCell ref="D9:D12"/>
-    <mergeCell ref="C9:C12"/>
-    <mergeCell ref="A9:A12"/>
-    <mergeCell ref="B9:B12"/>
-    <mergeCell ref="G9:G12"/>
+    <mergeCell ref="I9:I11"/>
+    <mergeCell ref="J9:J11"/>
+    <mergeCell ref="G9:G11"/>
+    <mergeCell ref="D9:D11"/>
     <mergeCell ref="C6:C8"/>
-    <mergeCell ref="I9:I12"/>
     <mergeCell ref="D4:F4"/>
     <mergeCell ref="J4:J5"/>
+    <mergeCell ref="A9:A11"/>
     <mergeCell ref="G4:I4"/>
+    <mergeCell ref="B9:B11"/>
     <mergeCell ref="J6:J8"/>
     <mergeCell ref="A4:C4"/>
     <mergeCell ref="A6:A8"/>
+    <mergeCell ref="C9:C11"/>
     <mergeCell ref="B6:B8"/>
     <mergeCell ref="F6:F8"/>
   </mergeCells>
@@ -2140,7 +2125,7 @@
       </c>
       <c r="F17" s="12" t="inlineStr">
         <is>
-          <t>Smart**</t>
+          <t>Excluded - specialty TCI/anaesthesia pump</t>
         </is>
       </c>
       <c r="G17" s="21" t="inlineStr">
@@ -2165,12 +2150,12 @@
       </c>
       <c r="K17" s="13" t="inlineStr">
         <is>
-          <t>ADD to Syringe-Smart**</t>
+          <t>EXCLUDED from market scope (specialty TCI / anaesthesia pump, per project team)</t>
         </is>
       </c>
       <c r="L17" s="13" t="inlineStr">
         <is>
-          <t>Anaesthesia (TCI) niche pump.</t>
+          <t>Would be Smart** on features (drug library; WiFi variant), but sits in the specialty anaesthesia segment, not general infusion.</t>
         </is>
       </c>
       <c r="M17" s="13" t="inlineStr">
@@ -3655,10 +3640,14 @@
       </c>
       <c r="E27" s="13" t="inlineStr">
         <is>
-          <t>ADDED</t>
-        </is>
-      </c>
-      <c r="F27" s="13" t="inlineStr"/>
+          <t>EXCLUDED</t>
+        </is>
+      </c>
+      <c r="F27" s="13" t="inlineStr">
+        <is>
+          <t>Specialty TCI/anaesthesia pump - out of market scope; keep for reference only</t>
+        </is>
+      </c>
     </row>
     <row r="28">
       <c r="A28" s="13" t="inlineStr">
@@ -3771,10 +3760,14 @@
       </c>
       <c r="E31" s="13" t="inlineStr">
         <is>
-          <t>ADDED (peach)</t>
-        </is>
-      </c>
-      <c r="F31" s="13" t="inlineStr"/>
+          <t>EXCLUDED</t>
+        </is>
+      </c>
+      <c r="F31" s="13" t="inlineStr">
+        <is>
+          <t>Specialty TCI/anaesthesia pump - out of market scope</t>
+        </is>
+      </c>
     </row>
     <row r="32">
       <c r="A32" s="13" t="inlineStr">
@@ -4132,7 +4125,7 @@
     <row r="3" ht="42" customHeight="1">
       <c r="A3" s="33" t="inlineStr">
         <is>
-          <t>1. Scope: India market, B. Braun and Fresenius Kabi; syringe and volumetric (large-volume) pumps. BD and Baxter skipped per instruction. Checked October 2026.</t>
+          <t>1. Scope: India market, B. Braun and Fresenius Kabi; general-purpose syringe and volumetric (large-volume) pumps. Specialty anaesthesia/TCI pumps (e.g., Agilia SP TIVA) excluded. BD and Baxter skipped per instruction. Checked October 2026.</t>
         </is>
       </c>
     </row>
